--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\git CF\Computer-Fundumental\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9270" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -295,6 +295,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -304,9 +307,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Calculation" xfId="3" builtinId="22"/>
@@ -315,43 +315,7 @@
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -361,96 +325,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <border>
@@ -765,31 +639,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:4" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" spans="1:4" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
@@ -803,7 +677,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1294025</v>
       </c>
@@ -815,7 +689,7 @@
       </c>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1294111</v>
       </c>
@@ -825,7 +699,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1294118</v>
       </c>
@@ -835,7 +709,7 @@
       <c r="C6" s="7"/>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1294174</v>
       </c>
@@ -845,7 +719,7 @@
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1294187</v>
       </c>
@@ -855,7 +729,7 @@
       <c r="C8" s="7"/>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1294343</v>
       </c>
@@ -865,7 +739,7 @@
       <c r="C9" s="7"/>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1294428</v>
       </c>
@@ -875,7 +749,7 @@
       <c r="C10" s="7"/>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1294544</v>
       </c>
@@ -885,7 +759,7 @@
       <c r="C11" s="7"/>
       <c r="D11" s="6"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1294563</v>
       </c>
@@ -895,7 +769,7 @@
       <c r="C12" s="7"/>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1294623</v>
       </c>
@@ -905,7 +779,7 @@
       <c r="C13" s="7"/>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1294647</v>
       </c>
@@ -915,7 +789,7 @@
       <c r="C14" s="7"/>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1294698</v>
       </c>
@@ -925,7 +799,7 @@
       <c r="C15" s="7"/>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1294711</v>
       </c>
@@ -935,7 +809,7 @@
       <c r="C16" s="7"/>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1294725</v>
       </c>
@@ -945,7 +819,7 @@
       <c r="C17" s="7"/>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1294124</v>
       </c>
@@ -953,7 +827,7 @@
       <c r="C18" s="7"/>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
     </row>
   </sheetData>
@@ -977,7 +851,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <conditionalFormatting sqref="A1">
     <cfRule type="dataBar" priority="1">
@@ -1017,24 +891,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
         <v>50</v>
       </c>
       <c r="B2">
@@ -1053,8 +927,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
         <v>255</v>
       </c>
       <c r="B3">
@@ -1073,8 +947,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
         <v>60</v>
       </c>
       <c r="B4">
@@ -1093,8 +967,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
         <v>105</v>
       </c>
       <c r="B5">
@@ -1113,8 +987,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
         <v>70</v>
       </c>
       <c r="B6">
@@ -1133,8 +1007,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
         <v>75</v>
       </c>
       <c r="B7">
@@ -1150,8 +1024,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
         <v>120</v>
       </c>
       <c r="B8">
@@ -1167,8 +1041,8 @@
         <v>Bodrul</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
         <v>85</v>
       </c>
       <c r="B9">
@@ -1184,8 +1058,8 @@
         <v>Bodrul</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
         <v>190</v>
       </c>
       <c r="B10">
@@ -1201,8 +1075,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
         <v>95</v>
       </c>
       <c r="B11">
@@ -1218,8 +1092,8 @@
         <v>Bodrul</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
         <v>100</v>
       </c>
       <c r="B12">
@@ -1235,8 +1109,8 @@
         <v>Bodrul</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
         <v>205</v>
       </c>
       <c r="B13">
@@ -1252,8 +1126,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
         <v>160</v>
       </c>
       <c r="B14">
@@ -1269,8 +1143,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
         <v>165</v>
       </c>
       <c r="B15">
@@ -1286,8 +1160,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
         <v>170</v>
       </c>
       <c r="B16">
@@ -1303,8 +1177,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
         <v>175</v>
       </c>
       <c r="B17">
@@ -1320,8 +1194,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="11">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
         <v>180</v>
       </c>
       <c r="B18">
@@ -1337,8 +1211,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="11">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
         <v>185</v>
       </c>
       <c r="B19">
@@ -1354,8 +1228,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="11">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
         <v>190</v>
       </c>
       <c r="B20">
@@ -1371,8 +1245,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
         <v>195</v>
       </c>
       <c r="B21">
@@ -1388,8 +1262,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
         <v>200</v>
       </c>
       <c r="B22">
@@ -1405,8 +1279,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="11">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
         <v>205</v>
       </c>
       <c r="B23">
@@ -1422,8 +1296,8 @@
         <v>PK</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
         <v>210</v>
       </c>
       <c r="B24">
@@ -1439,8 +1313,8 @@
         <v>Jui</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="11">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
         <v>215</v>
       </c>
       <c r="B25">
@@ -1456,8 +1330,8 @@
         <v>Jui</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="11">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
         <v>220</v>
       </c>
       <c r="B26">
@@ -1473,8 +1347,8 @@
         <v>Jui</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="11">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
         <v>225</v>
       </c>
       <c r="B27">
@@ -1490,8 +1364,8 @@
         <v>Jui</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="11">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
         <v>231.47692307692299</v>
       </c>
       <c r="B28">
@@ -1507,8 +1381,8 @@
         <v>Jui</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="11">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
         <v>236.92820512820501</v>
       </c>
       <c r="B29">
@@ -1524,8 +1398,8 @@
         <v>Jui</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="11">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
         <v>242.379487179487</v>
       </c>
       <c r="B30">
@@ -1541,8 +1415,8 @@
         <v>Miskatul</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="11">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
         <v>247.83076923076899</v>
       </c>
       <c r="B31">
@@ -1558,8 +1432,8 @@
         <v>Miskatul</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="11">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
         <v>253.28205128205099</v>
       </c>
       <c r="B32">
@@ -1575,8 +1449,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="11">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
         <v>258.73333333333397</v>
       </c>
       <c r="B33">
@@ -1592,8 +1466,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="11">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
         <v>264.184615384616</v>
       </c>
       <c r="B34">
@@ -1609,8 +1483,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="11">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
         <v>269.63589743589802</v>
       </c>
       <c r="B35">
@@ -1626,8 +1500,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="11">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
         <v>275.08717948717998</v>
       </c>
       <c r="B36">
@@ -1643,8 +1517,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="11">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
         <v>280.538461538462</v>
       </c>
       <c r="B37">
@@ -1660,8 +1534,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="11">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
         <v>285.98974358974402</v>
       </c>
       <c r="B38">
@@ -1677,8 +1551,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="11">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
         <v>291.44102564102599</v>
       </c>
       <c r="B39">
@@ -1694,8 +1568,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="11">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
         <v>296.89230769230801</v>
       </c>
       <c r="B40">
@@ -1711,8 +1585,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="11">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
         <v>254</v>
       </c>
       <c r="B41">
@@ -1728,8 +1602,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="11">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="8">
         <v>457</v>
       </c>
       <c r="B42">
@@ -1745,8 +1619,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="11">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
         <v>8</v>
       </c>
       <c r="B43">
@@ -1762,8 +1636,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="11">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
         <v>77</v>
       </c>
       <c r="B44">
@@ -1779,8 +1653,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="11">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
         <v>78</v>
       </c>
       <c r="B45">
@@ -1796,8 +1670,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="11">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
         <v>45</v>
       </c>
       <c r="B46">
@@ -1813,8 +1687,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="11">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
         <v>47</v>
       </c>
       <c r="B47">
@@ -1830,8 +1704,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="11">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
         <v>445</v>
       </c>
       <c r="B48">
@@ -1847,8 +1721,8 @@
         <v>Rehana</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="11">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
         <v>45</v>
       </c>
       <c r="B49">
@@ -1864,8 +1738,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="11">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
         <v>15</v>
       </c>
       <c r="B50">
@@ -1881,8 +1755,8 @@
         <v>Emon</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="11">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
         <v>45</v>
       </c>
       <c r="B51">
@@ -1900,13 +1774,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B51">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>2.5</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>3.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
